--- a/entertainment_forms/015_performance_arts_fellowship_application_form--entertainment_forms.xlsx
+++ b/entertainment_forms/015_performance_arts_fellowship_application_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'artist_or_organization'}</t>
+          <t>artist_or_organization</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Artist or Organization'}</t>
+          <t>Artist or Organization</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'theater'}</t>
+          <t>theater</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Theater'}</t>
+          <t>Theater</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'residency_grant'}</t>
+          <t>residency_grant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Residency Grant'}</t>
+          <t>Residency Grant</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'production_grant'}</t>
+          <t>production_grant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Production Grant'}</t>
+          <t>Production Grant</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'undetermined'}</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Undetermined'}</t>
+          <t>Undetermined</t>
         </is>
       </c>
     </row>
